--- a/artfynd/A 59762-2024 artfynd.xlsx
+++ b/artfynd/A 59762-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62062999</v>
+        <v>110244448</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långstrandberget, Jmt</t>
+          <t>Ammerberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540528.0499915375</v>
+        <v>540350</v>
       </c>
       <c r="R2" t="n">
-        <v>7017565.61873303</v>
+        <v>7017542</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Endast mycel Långstrandberget, utanför reservatsförslaget</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,40 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Mark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62062998</v>
+        <v>110244460</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långstrandberget, Jmt</t>
+          <t>Ammerberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540515.9869784142</v>
+        <v>540383</v>
       </c>
       <c r="R3" t="n">
-        <v>7017557.366514853</v>
+        <v>7017728</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Endast mycel Långstrandberget, utanför reservatsförslaget</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,77 +853,61 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Mark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1898139</v>
+        <v>110244461</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långstrandberget, utanför reservatsförslaget, Jmt</t>
+          <t>Ammerberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540652.9988752321</v>
+        <v>540335</v>
       </c>
       <c r="R4" t="n">
-        <v>7017627.046674918</v>
+        <v>7017652</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,45 +950,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Fuktig svacka med grandominans</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2052908</v>
+        <v>110244464</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,36 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långstrandberget, utanför reservatsförslaget, Jmt</t>
+          <t>Ammerberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540652.9988752321</v>
+        <v>540294</v>
       </c>
       <c r="R5" t="n">
-        <v>7017627.046674918</v>
+        <v>7017652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,82 +1047,61 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Fuktig svacka med grandominans</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>817369</v>
+        <v>110244471</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långstrandberget, utanför reservatsförslaget, Jmt</t>
+          <t>Ammerberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540652.9988752321</v>
+        <v>540209</v>
       </c>
       <c r="R6" t="n">
-        <v>7017627.046674918</v>
+        <v>7017598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2007-10-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,67 +1144,48 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Fuktig svacka med grandominans</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110244477</v>
+        <v>110244488</v>
       </c>
       <c r="B7" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1351,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540090.8704951104</v>
+        <v>540104</v>
       </c>
       <c r="R7" t="n">
-        <v>7017679.842298028</v>
+        <v>7017857</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1384,19 +1228,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110244456</v>
+        <v>110244492</v>
       </c>
       <c r="B8" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>504</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1463,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540463.864117901</v>
+        <v>540022</v>
       </c>
       <c r="R8" t="n">
-        <v>7017724.561935919</v>
+        <v>7017782</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1496,19 +1325,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1535,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110244488</v>
+        <v>110244498</v>
       </c>
       <c r="B9" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>504</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1575,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540103.5282793558</v>
+        <v>540011</v>
       </c>
       <c r="R9" t="n">
-        <v>7017857.293999643</v>
+        <v>7017700</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,19 +1422,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,50 +1451,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110244467</v>
+        <v>817369</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ammerberget, Jmt</t>
+          <t>Långstrandberget, utanför reservatsförslaget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540208.5950375149</v>
+        <v>540653</v>
       </c>
       <c r="R10" t="n">
-        <v>7017598.511059366</v>
+        <v>7017627</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1717,22 +1518,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,66 +1534,75 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Fuktig svacka med grandominans</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Salix</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110244476</v>
+        <v>62062998</v>
       </c>
       <c r="B11" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ammerberget, Jmt</t>
+          <t>Långstrandberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540090.8704951104</v>
+        <v>540516</v>
       </c>
       <c r="R11" t="n">
-        <v>7017679.842298028</v>
+        <v>7017557</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,22 +1629,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Endast mycel Långstrandberget, utanför reservatsförslaget</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,66 +1650,70 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110244465</v>
+        <v>62062999</v>
       </c>
       <c r="B12" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ammerberget, Jmt</t>
+          <t>Långstrandberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540293.9965806871</v>
+        <v>540528</v>
       </c>
       <c r="R12" t="n">
-        <v>7017651.78021936</v>
+        <v>7017566</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,22 +1740,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Endast mycel Långstrandberget, utanför reservatsförslaget</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,53 +1761,57 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110244464</v>
+        <v>110244456</v>
       </c>
       <c r="B13" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>504</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2023,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540293.9965806871</v>
+        <v>540464</v>
       </c>
       <c r="R13" t="n">
-        <v>7017651.78021936</v>
+        <v>7017725</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2056,19 +1854,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,37 +1883,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110244454</v>
+        <v>110244477</v>
       </c>
       <c r="B14" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2135,10 +1918,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540570.581590509</v>
+        <v>540091</v>
       </c>
       <c r="R14" t="n">
-        <v>7017694.856452738</v>
+        <v>7017680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,19 +1951,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2207,15 +1980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110244450</v>
+        <v>1898139</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,16 +2009,18 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ammerberget, Jmt</t>
+          <t>Långstrandberget, utanför reservatsförslaget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540351.1206479629</v>
+        <v>540653</v>
       </c>
       <c r="R15" t="n">
-        <v>7017624.146002979</v>
+        <v>7017627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2277,22 +2047,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,53 +2063,62 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Fuktig svacka med grandominans</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110244471</v>
+        <v>110244450</v>
       </c>
       <c r="B16" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2359,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540208.5950375149</v>
+        <v>540351</v>
       </c>
       <c r="R16" t="n">
-        <v>7017598.511059366</v>
+        <v>7017624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2392,19 +2161,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,37 +2190,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110244461</v>
+        <v>110244452</v>
       </c>
       <c r="B17" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2471,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540334.9960684387</v>
+        <v>540636</v>
       </c>
       <c r="R17" t="n">
-        <v>7017652.29402288</v>
+        <v>7017614</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2504,19 +2258,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2543,37 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110244453</v>
+        <v>110244473</v>
       </c>
       <c r="B18" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2583,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540570.581590509</v>
+        <v>540187</v>
       </c>
       <c r="R18" t="n">
-        <v>7017694.856452738</v>
+        <v>7017713</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2616,19 +2355,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2655,37 +2384,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110244500</v>
+        <v>110244476</v>
       </c>
       <c r="B19" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2695,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540053.9374314109</v>
+        <v>540091</v>
       </c>
       <c r="R19" t="n">
-        <v>7017678.48223532</v>
+        <v>7017680</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2728,19 +2452,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2767,50 +2481,47 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110244452</v>
+        <v>2052908</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ammerberget, Jmt</t>
+          <t>Långstrandberget, utanför reservatsförslaget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540636.4934405042</v>
+        <v>540653</v>
       </c>
       <c r="R20" t="n">
-        <v>7017613.78792325</v>
+        <v>7017627</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2837,22 +2548,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2863,31 +2564,40 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Fuktig svacka med grandominans</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110244460</v>
+        <v>110244470</v>
       </c>
       <c r="B21" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,21 +2605,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>504</v>
+        <v>219874</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2919,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540383.1677372659</v>
+        <v>540209</v>
       </c>
       <c r="R21" t="n">
-        <v>7017727.597815084</v>
+        <v>7017598</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2952,19 +2662,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,15 +2691,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110244470</v>
+        <v>110244453</v>
       </c>
       <c r="B22" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3007,21 +2702,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>219880</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3031,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540208.5950375149</v>
+        <v>540570</v>
       </c>
       <c r="R22" t="n">
-        <v>7017598.511059366</v>
+        <v>7017695</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3064,19 +2759,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3103,37 +2788,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110244473</v>
+        <v>110244490</v>
       </c>
       <c r="B23" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3143,10 +2823,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540187.3318486884</v>
+        <v>540032</v>
       </c>
       <c r="R23" t="n">
-        <v>7017713.445532076</v>
+        <v>7017770</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3176,19 +2856,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3215,15 +2885,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110244448</v>
+        <v>110244479</v>
       </c>
       <c r="B24" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,21 +2896,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>504</v>
+        <v>221725</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3255,10 +2920,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540350.3568471448</v>
+        <v>540034</v>
       </c>
       <c r="R24" t="n">
-        <v>7017541.334309023</v>
+        <v>7017707</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3288,19 +2953,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3327,15 +2982,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110244469</v>
+        <v>110244489</v>
       </c>
       <c r="B25" t="n">
-        <v>101141</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3343,21 +2993,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222002</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3367,10 +3017,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540208.5950375149</v>
+        <v>540032</v>
       </c>
       <c r="R25" t="n">
-        <v>7017598.511059366</v>
+        <v>7017770</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3400,19 +3050,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3436,6 +3076,491 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>110244469</v>
+      </c>
+      <c r="B26" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ammerberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>540209</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7017598</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>110244465</v>
+      </c>
+      <c r="B27" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ammerberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>540294</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7017652</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>110244454</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ammerberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>540570</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7017695</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>110244467</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ammerberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>540209</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7017598</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>110244500</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ammerberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>540054</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7017679</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59762-2024 artfynd.xlsx
+++ b/artfynd/A 59762-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244448</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244460</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244461</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244464</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244471</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244488</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244492</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244498</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1561,6 +1606,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/817369</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62062998</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62062999</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1880,6 +1940,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244456</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1977,6 +2042,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244477</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1898139</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244450</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2284,6 +2364,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244452</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2381,6 +2466,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244473</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2478,6 +2568,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244476</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2052908</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2688,6 +2788,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244470</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2785,6 +2890,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244453</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2882,6 +2992,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244490</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2979,6 +3094,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244479</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3076,6 +3196,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244489</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3173,6 +3298,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244469</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3270,6 +3400,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244465</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3367,6 +3502,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244454</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3464,6 +3604,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244467</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3561,8 +3706,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110244500</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>